--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="219">
   <si>
     <t xml:space="preserve">Song</t>
   </si>
@@ -616,15 +616,15 @@
     <t xml:space="preserve"> - Backwater</t>
   </si>
   <si>
+    <t xml:space="preserve">Pretty Woman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found Out About U</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hemorrhage</t>
   </si>
   <si>
-    <t xml:space="preserve">Found Out About U ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Mr Jones &amp; Me</t>
-  </si>
-  <si>
     <t xml:space="preserve">The Power of Love</t>
   </si>
   <si>
@@ -634,22 +634,13 @@
     <t xml:space="preserve"> - Long Way Down</t>
   </si>
   <si>
+    <t xml:space="preserve">Bad Case of Loving</t>
+  </si>
+  <si>
     <t xml:space="preserve">Working For Week</t>
   </si>
   <si>
-    <t xml:space="preserve">Cocaine ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Bad Case of Loving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">She’s A Beauty</t>
-  </si>
-  <si>
     <t xml:space="preserve">Beast Of Burden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Own Worst En ↓</t>
   </si>
   <si>
     <t xml:space="preserve">Mary Jane's Last</t>
@@ -659,13 +650,31 @@
 Lovesong, SemiCh</t>
   </si>
   <si>
+    <t xml:space="preserve">Champ Supernova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She’s A Beauty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Own Worst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't You Forget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semi-Charmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Own Worst En ↓</t>
+  </si>
+  <si>
     <t xml:space="preserve"> - Don't You Forget</t>
   </si>
   <si>
-    <t xml:space="preserve">Champ Supernova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semi-Charmed</t>
+    <t xml:space="preserve">Found Out About U ↓</t>
   </si>
   <si>
     <t xml:space="preserve">--- Set 2 ---</t>
@@ -674,7 +683,16 @@
     <t xml:space="preserve"> - All For You</t>
   </si>
   <si>
+    <t xml:space="preserve"> - Mr Jones &amp; Me</t>
+  </si>
+  <si>
     <t xml:space="preserve">Blitzkreig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cocaine ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Bad Case of Loving</t>
   </si>
 </sst>
 </file>
@@ -684,7 +702,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -740,6 +758,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i val="true"/>
@@ -832,7 +856,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -909,6 +933,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -917,23 +949,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2317,8 +2345,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="32.53515625" defaultRowHeight="34.35" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultColWidth="32.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.28"/>
@@ -2395,8 +2423,8 @@
       <c r="A7" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>162</v>
+      <c r="B7" s="17" t="s">
+        <v>195</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>64</v>
@@ -2404,32 +2432,30 @@
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>170</v>
+        <v>128</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>20</v>
-      </c>
+      <c r="B9" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>169</v>
+      <c r="B10" s="21" t="s">
+        <v>162</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>67</v>
@@ -2439,8 +2465,8 @@
       <c r="A11" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>199</v>
+      <c r="B11" s="22" t="s">
+        <v>170</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>153</v>
@@ -2450,8 +2476,8 @@
       <c r="A12" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>173</v>
+      <c r="B12" s="22" t="s">
+        <v>117</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>114</v>
@@ -2459,24 +2485,24 @@
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>201</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2484,32 +2510,46 @@
         <v>177</v>
       </c>
       <c r="B15" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="16" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="D15" s="21"/>
-    </row>
-    <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
+      <c r="C17" s="25"/>
+    </row>
+    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20"/>
+      <c r="B18" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="B16" s="16" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="16" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="16" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C17" s="24"/>
-    </row>
-    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21"/>
-    </row>
-    <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -2539,9 +2579,9 @@
         <v>35</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="C1" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2552,7 +2592,7 @@
       <c r="B2" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>170</v>
       </c>
     </row>
@@ -2560,10 +2600,10 @@
       <c r="A3" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="20" t="s">
         <v>209</v>
       </c>
     </row>
@@ -2572,9 +2612,9 @@
         <v>75</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="C4" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2583,7 +2623,7 @@
         <v>190</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>153</v>
@@ -2594,7 +2634,7 @@
         <v>192</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>114</v>
@@ -2602,34 +2642,34 @@
     </row>
     <row r="7" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>211</v>
+      <c r="A8" s="20" t="s">
+        <v>214</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>203</v>
+      <c r="C8" s="20" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C9" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2641,7 +2681,7 @@
         <v>189</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2652,7 +2692,7 @@
         <v>61</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2665,23 +2705,23 @@
     </row>
     <row r="13" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="21"/>
+      <c r="C14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="227">
   <si>
     <t xml:space="preserve">Song</t>
   </si>
@@ -153,15 +153,6 @@
     <t xml:space="preserve">Don Henley</t>
   </si>
   <si>
-    <t xml:space="preserve">Burden In My Hand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B (down a step)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soundgarden</t>
-  </si>
-  <si>
     <t xml:space="preserve">Champagne Supernova</t>
   </si>
   <si>
@@ -401,6 +392,19 @@
     <t xml:space="preserve">Tom Petty</t>
   </si>
   <si>
+    <t xml:space="preserve">Midnight Rider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D – Gm C D
+S: C Bb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allman Brothers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Miss You</t>
   </si>
   <si>
@@ -471,6 +475,15 @@
     <t xml:space="preserve">Huey Lewis</t>
   </si>
   <si>
+    <t xml:space="preserve">Pretty Woman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A F#m D E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van Halen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pride</t>
   </si>
   <si>
@@ -595,9 +608,15 @@
     <t xml:space="preserve">Nothin’ But A Good</t>
   </si>
   <si>
+    <t xml:space="preserve">My Own Worst</t>
+  </si>
+  <si>
     <t xml:space="preserve">A Girl Like You ↓</t>
   </si>
   <si>
+    <t xml:space="preserve">Would</t>
+  </si>
+  <si>
     <t xml:space="preserve">I Was Made For</t>
   </si>
   <si>
@@ -607,6 +626,12 @@
     <t xml:space="preserve">Hold The Line</t>
   </si>
   <si>
+    <t xml:space="preserve">Let’s Go / She’s Beauty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long Train Running</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santeria ↓</t>
   </si>
   <si>
@@ -616,77 +641,102 @@
     <t xml:space="preserve"> - Backwater</t>
   </si>
   <si>
-    <t xml:space="preserve">Pretty Woman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Found Out About U</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hemorrhage</t>
   </si>
   <si>
+    <t xml:space="preserve">Summer of 69</t>
+  </si>
+  <si>
     <t xml:space="preserve">The Power of Love</t>
   </si>
   <si>
+    <t xml:space="preserve">Cover Me / Long WD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low / Midnight Rdr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sirius / Blue Cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad Case of Loving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary Jane's Last</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champ Supernova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't You Forget</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">All4U, Beast, Come Together, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Cumbersome, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Santa Mon
+Semicharm, Watchtower</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Working For Week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semi-Charmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She’s A Beauty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Own Worst En ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Don't You Forget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found Out About U ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- Set 2 ---</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - All For You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beast Of Burden</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Mr Jones &amp; Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blitzkreig</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cover Me ↓</t>
   </si>
   <si>
     <t xml:space="preserve"> - Long Way Down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bad Case of Loving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working For Week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beast Of Burden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary Jane's Last</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X: All4U, Blitz, Jealousy
-Lovesong, SemiCh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Champ Supernova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Let’s Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">She’s A Beauty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Own Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't You Forget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semi-Charmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Own Worst En ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Don't You Forget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Found Out About U ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">--- Set 2 ---</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - All For You</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Mr Jones &amp; Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blitzkreig</t>
   </si>
   <si>
     <t xml:space="preserve">Cocaine ↓</t>
@@ -702,7 +752,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -766,9 +816,20 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -776,6 +837,7 @@
     <font>
       <i val="true"/>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -789,7 +851,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -799,19 +861,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFEEEEEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEEEEE"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDDDDD"/>
-        <bgColor rgb="FFEEEEEE"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -856,7 +906,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -913,19 +963,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -933,35 +979,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -974,66 +1020,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFEEEEEE"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFDDDDDD"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1148,7 +1134,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.73"/>
@@ -1384,14 +1370,12 @@
         <v>42</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>39</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D13" s="8"/>
       <c r="E13" s="7" t="s">
         <v>43</v>
       </c>
@@ -1407,19 +1391,19 @@
         <v>7</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>7</v>
@@ -1429,25 +1413,25 @@
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="7" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>51</v>
@@ -1461,7 +1445,7 @@
         <v>11</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="7" t="s">
@@ -1479,7 +1463,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="7" t="s">
@@ -1494,10 +1478,10 @@
         <v>58</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="7" t="s">
@@ -1512,12 +1496,12 @@
         <v>61</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>149</v>
-      </c>
-      <c r="D20" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="D20" s="10"/>
       <c r="E20" s="7" t="s">
         <v>62</v>
       </c>
@@ -1530,48 +1514,48 @@
         <v>64</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>122</v>
-      </c>
-      <c r="D22" s="10"/>
+        <v>111</v>
+      </c>
+      <c r="D22" s="8"/>
       <c r="E22" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="D23" s="8"/>
+        <v>77</v>
+      </c>
+      <c r="D23" s="10"/>
       <c r="E23" s="7" t="s">
         <v>73</v>
       </c>
@@ -1584,12 +1568,12 @@
         <v>75</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="D24" s="10"/>
+        <v>145</v>
+      </c>
+      <c r="D24" s="8"/>
       <c r="E24" s="7" t="s">
         <v>76</v>
       </c>
@@ -1602,10 +1586,10 @@
         <v>78</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="7" t="s">
@@ -1620,101 +1604,101 @@
         <v>81</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>135</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="C26" s="7"/>
       <c r="D26" s="8"/>
       <c r="E26" s="7" t="s">
         <v>82</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="7"/>
+        <v>11</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>110</v>
+      </c>
       <c r="D27" s="8"/>
       <c r="E27" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>110</v>
-      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="7"/>
+      <c r="F28" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="7"/>
+      <c r="C29" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>90</v>
+      </c>
       <c r="F29" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>152</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>39</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="D30" s="8"/>
       <c r="E30" s="7" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="7" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1722,12 +1706,14 @@
         <v>96</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="D32" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="E32" s="7" t="s">
         <v>97</v>
       </c>
@@ -1743,11 +1729,9 @@
         <v>11</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>39</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="D33" s="8"/>
       <c r="E33" s="7" t="s">
         <v>100</v>
       </c>
@@ -1760,12 +1744,12 @@
         <v>102</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>128</v>
-      </c>
-      <c r="D34" s="8"/>
+        <v>176</v>
+      </c>
+      <c r="D34" s="10"/>
       <c r="E34" s="7" t="s">
         <v>103</v>
       </c>
@@ -1781,9 +1765,9 @@
         <v>7</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>176</v>
-      </c>
-      <c r="D35" s="10"/>
+        <v>168</v>
+      </c>
+      <c r="D35" s="8"/>
       <c r="E35" s="7" t="s">
         <v>106</v>
       </c>
@@ -1796,10 +1780,10 @@
         <v>108</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="7" t="s">
@@ -1814,12 +1798,12 @@
         <v>111</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>140</v>
-      </c>
-      <c r="D37" s="8"/>
+        <v>174</v>
+      </c>
+      <c r="D37" s="12"/>
       <c r="E37" s="7" t="s">
         <v>112</v>
       </c>
@@ -1832,15 +1816,15 @@
         <v>114</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>174</v>
-      </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>115</v>
       </c>
+      <c r="E38" s="7"/>
       <c r="F38" s="9" t="s">
         <v>116</v>
       </c>
@@ -1850,15 +1834,15 @@
         <v>117</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>142</v>
-      </c>
-      <c r="D39" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E39" s="7"/>
       <c r="F39" s="9" t="s">
         <v>119</v>
       </c>
@@ -1868,22 +1852,20 @@
         <v>120</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>85</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C40" s="7"/>
       <c r="D40" s="8"/>
       <c r="E40" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>7</v>
@@ -1893,7 +1875,7 @@
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>31</v>
@@ -1901,7 +1883,7 @@
     </row>
     <row r="42" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>11</v>
@@ -1911,15 +1893,15 @@
       </c>
       <c r="D42" s="10"/>
       <c r="E42" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>7</v>
@@ -1929,15 +1911,15 @@
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>7</v>
@@ -1947,15 +1929,15 @@
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>11</v>
@@ -1965,15 +1947,15 @@
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>7</v>
@@ -1985,15 +1967,15 @@
         <v>39</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>7</v>
@@ -2003,15 +1985,15 @@
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>11</v>
@@ -2021,313 +2003,331 @@
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>106</v>
-      </c>
-      <c r="D49" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="14" t="s">
         <v>39</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>127</v>
-      </c>
-      <c r="D51" s="8"/>
+        <v>132</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="E51" s="7" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>152</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D52" s="10"/>
+        <v>127</v>
+      </c>
+      <c r="D52" s="8"/>
       <c r="E52" s="7" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="14" t="s">
-        <v>156</v>
+      <c r="A53" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D53" s="10"/>
+      <c r="E53" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="7" t="n">
         <v>91</v>
-      </c>
-      <c r="D53" s="8"/>
-      <c r="E53" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>102</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>140</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>118</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="D55" s="8"/>
       <c r="E55" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="D56" s="8"/>
+        <v>140</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="E56" s="7" t="s">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="7" t="s">
-        <v>168</v>
+        <v>8</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E58" s="7"/>
+        <v>115</v>
+      </c>
+      <c r="D58" s="8"/>
+      <c r="E58" s="7" t="s">
+        <v>172</v>
+      </c>
       <c r="F58" s="9" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>171</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E59" s="7"/>
       <c r="F59" s="9" t="s">
-        <v>172</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>139</v>
-      </c>
-      <c r="D60" s="8"/>
+        <v>124</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="E60" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E61" s="7"/>
+        <v>177</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>139</v>
+      </c>
+      <c r="D61" s="8"/>
+      <c r="E61" s="7" t="s">
+        <v>178</v>
+      </c>
       <c r="F61" s="9" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>160</v>
-      </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="7" t="s">
-        <v>178</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E62" s="7"/>
       <c r="F62" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B64" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="D64" s="8"/>
+      <c r="E64" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B65" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C65" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D65" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E64" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D65" s="10"/>
-      <c r="F65" s="1"/>
+      <c r="E65" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D66" s="10"/>
       <c r="F66" s="1"/>
+    </row>
+    <row r="67" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D67" s="10"/>
+      <c r="F67" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2345,7 +2345,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="32.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.97"/>
@@ -2357,198 +2357,187 @@
       <c r="A1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>185</v>
+      <c r="B1" s="16" t="s">
+        <v>189</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>187</v>
+        <v>191</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>99</v>
+        <v>72</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>96</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>191</v>
+        <v>196</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>197</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>193</v>
+      <c r="A6" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>199</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>195</v>
+        <v>200</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>147</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>125</v>
+        <v>78</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C9" s="16"/>
+      <c r="A9" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>162</v>
+      <c r="A10" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>179</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>170</v>
+        <v>204</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>174</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>117</v>
+        <v>206</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>166</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>201</v>
+        <v>207</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>173</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="B15" s="21"/>
       <c r="C15" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="D15" s="20"/>
+        <v>209</v>
+      </c>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>204</v>
+      <c r="A16" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="22" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="C17" s="25"/>
-    </row>
-    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20"/>
-      <c r="B18" s="16" t="s">
-        <v>206</v>
-      </c>
-    </row>
+      <c r="C17" s="23"/>
+    </row>
+    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="16" t="s">
-        <v>207</v>
-      </c>
+      <c r="B19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="16" t="s">
-        <v>208</v>
-      </c>
+      <c r="B20" s="16"/>
+    </row>
+    <row r="27" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2579,125 +2568,125 @@
         <v>35</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="C1" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>170</v>
+        <v>75</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>209</v>
+        <v>194</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>67</v>
+        <v>214</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>190</v>
+      <c r="A5" s="17" t="s">
+        <v>198</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>48</v>
+        <v>217</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>214</v>
+      <c r="A8" s="18" t="s">
+        <v>219</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>201</v>
+        <v>124</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>111</v>
+        <v>221</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>10</v>
@@ -2705,30 +2694,30 @@
     </row>
     <row r="13" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>52</v>
+        <v>102</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="20"/>
+        <v>61</v>
+      </c>
+      <c r="C14" s="18"/>
     </row>
     <row r="15" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="234">
   <si>
     <t xml:space="preserve">Song</t>
   </si>
@@ -620,89 +620,281 @@
     <t xml:space="preserve">I Was Made For</t>
   </si>
   <si>
-    <t xml:space="preserve"> - All Right Now</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hold The Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Let’s Go / She’s Beauty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long Train Running</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santeria ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rockin' in the Free</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Backwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hemorrhage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summer of 69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Power of Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cover Me / Long WD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low / Midnight Rdr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sirius / Blue Cars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bad Case of Loving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary Jane's Last</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Champ Supernova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't You Forget</t>
-  </si>
-  <si>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">All4U, Beast, Come Together, </t>
+      <t xml:space="preserve"> All Right Now</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold The Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s Go ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long Train Running</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">→</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Cumbersome, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <sz val="16"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Santa Mon
-Semicharm, Watchtower</t>
+      <t xml:space="preserve"> She’s Beauty</t>
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Rockin' in the Free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santeria ↓</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Int </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">→ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Pretty Woman</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Inside Out </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">↓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Backwater</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">→ Cumbersome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemorrhage</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Summer of 69 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">↓</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The Power of Love</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Flagpole Sitta</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cover Me</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → LWD</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Low ↓</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sirius </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Blue Cars</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Midnight Rider</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad Case of Loving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary Jane's Last</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champ Supernova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't You Forget</t>
+  </si>
+  <si>
     <t xml:space="preserve">Working For Week</t>
   </si>
   <si>
+    <t xml:space="preserve"> - All Right Now</t>
+  </si>
+  <si>
     <t xml:space="preserve">Semi-Charmed</t>
   </si>
   <si>
@@ -710,6 +902,9 @@
   </si>
   <si>
     <t xml:space="preserve">My Own Worst En ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Backwater</t>
   </si>
   <si>
     <t xml:space="preserve"> - Don't You Forget</t>
@@ -816,20 +1011,19 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="10"/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -906,7 +1100,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -979,28 +1173,36 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2376,7 +2578,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="18" t="s">
         <v>194</v>
       </c>
       <c r="B3" s="16" t="s">
@@ -2398,10 +2600,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>197</v>
       </c>
       <c r="C5" s="16" t="s">
@@ -2409,7 +2611,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="21" t="s">
         <v>198</v>
       </c>
       <c r="B6" s="16" t="s">
@@ -2420,116 +2622,124 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="20" t="s">
         <v>200</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>102</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>78</v>
+      <c r="A8" s="18" t="s">
+        <v>203</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>126</v>
+      <c r="C8" s="19" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
         <v>129</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>203</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>179</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="18" t="s">
+      <c r="A11" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>205</v>
+      <c r="C11" s="18" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C12" s="16" t="s">
-        <v>45</v>
+      <c r="C12" s="19" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>47</v>
+        <v>211</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>114</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>207</v>
+        <v>47</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="C14" s="16" t="s">
-        <v>208</v>
+      <c r="C14" s="20" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="D15" s="18"/>
-    </row>
-    <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="22" t="s">
-        <v>211</v>
+      <c r="B16" s="22"/>
+      <c r="C16" s="16" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C17" s="23"/>
-    </row>
-    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="A17" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+    </row>
+    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+    </row>
     <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="16"/>
     </row>
@@ -2537,7 +2747,7 @@
       <c r="B20" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24"/>
+      <c r="A27" s="26"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2568,9 +2778,9 @@
         <v>35</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="C1" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2581,19 +2791,19 @@
       <c r="B2" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="20" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="B3" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>213</v>
+      <c r="C3" s="20" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2601,18 +2811,18 @@
         <v>72</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>157</v>
@@ -2620,10 +2830,10 @@
     </row>
     <row r="6" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>111</v>
@@ -2631,57 +2841,57 @@
     </row>
     <row r="7" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>219</v>
+      <c r="A8" s="20" t="s">
+        <v>226</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>220</v>
+      <c r="C8" s="20" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="C9" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>195</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>58</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2694,23 +2904,23 @@
     </row>
     <row r="13" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="20" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="18"/>
+      <c r="C14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="233">
   <si>
     <t xml:space="preserve">Song</t>
   </si>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">Nothin’ But A Good</t>
   </si>
   <si>
-    <t xml:space="preserve">My Own Worst</t>
+    <t xml:space="preserve">My Own Worst En</t>
   </si>
   <si>
     <t xml:space="preserve">A Girl Like You ↓</t>
@@ -617,58 +617,22 @@
     <t xml:space="preserve">Would</t>
   </si>
   <si>
-    <t xml:space="preserve">I Was Made For</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> All Right Now</t>
-    </r>
+    <t xml:space="preserve">I Was Made For Lv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ All Right Now</t>
   </si>
   <si>
     <t xml:space="preserve">Hold The Line</t>
   </si>
   <si>
-    <t xml:space="preserve">Let’s Go ↓</t>
+    <t xml:space="preserve">Let’s Go</t>
   </si>
   <si>
     <t xml:space="preserve">Long Train Running</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> She’s Beauty</t>
-    </r>
+    <t xml:space="preserve">She’s A Beauty</t>
   </si>
   <si>
     <t xml:space="preserve">Rockin' in the Free</t>
@@ -677,204 +641,40 @@
     <t xml:space="preserve">Santeria ↓</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Int </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">→ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Pretty Woman</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Inside Out </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">↓</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Backwater</t>
-    </r>
+    <t xml:space="preserve">Intr → Pretty Woman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inside Out ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ Backwater</t>
   </si>
   <si>
     <t xml:space="preserve">→ Cumbersome</t>
   </si>
   <si>
-    <t xml:space="preserve">Hemorrhage</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Summer of 69 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">↓</t>
-    </r>
+    <t xml:space="preserve">Hemorrhage in my</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer of 69 ↓</t>
   </si>
   <si>
     <t xml:space="preserve">The Power of Love</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Flagpole Sitta</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cover Me</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> → LWD</t>
-    </r>
+    <t xml:space="preserve">→ Flagpole Sitta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cover Me → Long WD</t>
   </si>
   <si>
     <t xml:space="preserve">Low ↓</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sirius </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Blue Cars</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Midnight Rider</t>
-    </r>
+    <t xml:space="preserve">Sirius → Blue Cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ Midnight Rider</t>
   </si>
   <si>
     <t xml:space="preserve">Bad Case of Loving</t>
@@ -896,9 +696,6 @@
   </si>
   <si>
     <t xml:space="preserve">Semi-Charmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">She’s A Beauty</t>
   </si>
   <si>
     <t xml:space="preserve">My Own Worst En ↓</t>
@@ -947,7 +744,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1005,22 +802,18 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="16"/>
@@ -1100,7 +893,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1173,14 +966,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1193,23 +978,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2578,7 +2359,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
         <v>194</v>
       </c>
       <c r="B3" s="16" t="s">
@@ -2600,10 +2381,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="18" t="s">
         <v>197</v>
       </c>
       <c r="C5" s="16" t="s">
@@ -2611,7 +2392,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="18" t="s">
         <v>198</v>
       </c>
       <c r="B6" s="16" t="s">
@@ -2622,7 +2403,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="18" t="s">
         <v>200</v>
       </c>
       <c r="B7" s="16" t="s">
@@ -2633,13 +2414,13 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="16" t="s">
         <v>203</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>204</v>
       </c>
     </row>
@@ -2647,7 +2428,7 @@
       <c r="A9" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="18" t="s">
         <v>205</v>
       </c>
       <c r="C9" s="16" t="s">
@@ -2666,13 +2447,13 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>208</v>
       </c>
     </row>
@@ -2683,7 +2464,7 @@
       <c r="B12" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>210</v>
       </c>
     </row>
@@ -2694,7 +2475,7 @@
       <c r="B13" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2705,7 +2486,7 @@
       <c r="B14" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="18" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2717,28 +2498,28 @@
       <c r="C15" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D15" s="20"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="22"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="16" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="24"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="16"/>
@@ -2747,7 +2528,7 @@
       <c r="B20" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26"/>
+      <c r="A27" s="23"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2780,7 +2561,7 @@
       <c r="B1" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2791,7 +2572,7 @@
       <c r="B2" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="18" t="s">
         <v>174</v>
       </c>
     </row>
@@ -2799,10 +2580,10 @@
       <c r="A3" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="18" t="s">
         <v>219</v>
       </c>
     </row>
@@ -2811,9 +2592,9 @@
         <v>72</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="C4" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2822,7 +2603,7 @@
         <v>200</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>157</v>
@@ -2830,10 +2611,10 @@
     </row>
     <row r="6" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>222</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>223</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>111</v>
@@ -2841,40 +2622,40 @@
     </row>
     <row r="7" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="C7" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
         <v>225</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>226</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>227</v>
+      <c r="C8" s="18" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="18" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>195</v>
@@ -2885,7 +2666,7 @@
     </row>
     <row r="11" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>58</v>
@@ -2904,23 +2685,23 @@
     </row>
     <row r="13" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="18" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="20"/>
+      <c r="C14" s="18"/>
     </row>
     <row r="15" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -608,7 +608,7 @@
     <t xml:space="preserve">Nothin’ But A Good</t>
   </si>
   <si>
-    <t xml:space="preserve">My Own Worst En</t>
+    <t xml:space="preserve">My Own Worst</t>
   </si>
   <si>
     <t xml:space="preserve">A Girl Like You ↓</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">Would</t>
   </si>
   <si>
-    <t xml:space="preserve">I Was Made For Lv</t>
+    <t xml:space="preserve">I Was Made For</t>
   </si>
   <si>
     <t xml:space="preserve">→ All Right Now</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">Santeria ↓</t>
   </si>
   <si>
-    <t xml:space="preserve">Intr → Pretty Woman</t>
+    <t xml:space="preserve">Int → Pretty Woman</t>
   </si>
   <si>
     <t xml:space="preserve">Inside Out ↓</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">Champ Supernova</t>
   </si>
   <si>
-    <t xml:space="preserve">Don't You Forget</t>
+    <t xml:space="preserve">Don't You Forget About</t>
   </si>
   <si>
     <t xml:space="preserve">Working For Week</t>
@@ -2331,9 +2331,9 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="32.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
